--- a/docs/ValueSet-ahip-demo-gender-identity.xlsx
+++ b/docs/ValueSet-ahip-demo-gender-identity.xlsx
@@ -10,13 +10,12 @@
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
   <si>
     <t>Property</t>
   </si>
@@ -45,13 +44,13 @@
     <t>Title</t>
   </si>
   <si>
-    <t>AHIP Gender</t>
+    <t>AHIP Gender Identity</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +86,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Based on HL7 Gender-Identity</t>
+    <t>Used as the answer options for the gender question in the SOGI and Relationship Status Section, capturing a patient's gender identity. Based on the HL7 Gender Identity value set</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -108,55 +107,52 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>male</t>
+    <t>446151000124109</t>
   </si>
   <si>
     <t>Man</t>
   </si>
   <si>
-    <t>female</t>
+    <t>446141000124107</t>
   </si>
   <si>
     <t>Woman</t>
   </si>
   <si>
-    <t>transgender-man</t>
+    <t>911621000124109</t>
   </si>
   <si>
     <t>Transgender Man</t>
   </si>
   <si>
-    <t>transgender-woman</t>
+    <t>911581000124109</t>
   </si>
   <si>
     <t>Transgender Woman</t>
   </si>
   <si>
-    <t>non-binary</t>
+    <t>33791000087105</t>
   </si>
   <si>
     <t>Non-Binary (neither exclusively male nor female)</t>
   </si>
   <si>
+    <t>911671000124105</t>
+  </si>
+  <si>
+    <t>Gender Fluid (non-fixed gender indentity that may change overtime)</t>
+  </si>
+  <si>
+    <t>911541000124103</t>
+  </si>
+  <si>
+    <t>Two Spirit (a person who has both a masculine and feminine spirit, traditionally used in Native American/Alaskan Native communities)</t>
+  </si>
+  <si>
     <t>System URI</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/gender-identity</t>
-  </si>
-  <si>
-    <t>#GF</t>
-  </si>
-  <si>
-    <t>Gender Fluid (non-fixed gender indentity that may change overtime)</t>
-  </si>
-  <si>
-    <t>TS</t>
-  </si>
-  <si>
-    <t>Two Spirit (a person who has both a masculine and feminine spirit, traditionally used in Native American/Alaskan Native communities)</t>
-  </si>
-  <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/ahip-demo-additional-gender-codes</t>
+    <t>http://snomed.info/sct</t>
   </si>
   <si>
     <t>PSIN</t>
@@ -171,7 +167,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/AHIPDemoAdditionalNullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
   </si>
   <si>
     <t>ASKU</t>
@@ -446,7 +442,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -503,18 +499,34 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -541,18 +553,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -565,10 +577,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -577,60 +589,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -649,10 +607,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -665,10 +623,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-demo-gender-identity.xlsx
+++ b/docs/ValueSet-ahip-demo-gender-identity.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -155,10 +155,13 @@
     <t>http://snomed.info/sct</t>
   </si>
   <si>
-    <t>PSIN</t>
-  </si>
-  <si>
-    <t>Please specify if not listed above</t>
+    <t>ASKU</t>
+  </si>
+  <si>
+    <t>I don't know</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v3-NullFlavor</t>
   </si>
   <si>
     <t>CNTR</t>
@@ -168,15 +171,6 @@
   </si>
   <si>
     <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
-  </si>
-  <si>
-    <t>ASKU</t>
-  </si>
-  <si>
-    <t>I don't know</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-NullFlavor</t>
   </si>
 </sst>
 </file>
@@ -536,7 +530,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -561,26 +555,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -607,10 +593,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -626,7 +612,7 @@
         <v>44</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-demo-gender-identity.xlsx
+++ b/docs/ValueSet-ahip-demo-gender-identity.xlsx
@@ -95,7 +95,9 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement.
+This material derives from the HL7 Terminology (THO). THO is copyright ©1989+ Health Level Seven International and is made available under the CC0 designation. For more licensing information see: https://terminology.hl7.org/license.html
+This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -140,7 +142,7 @@
     <t>911671000124105</t>
   </si>
   <si>
-    <t>Gender Fluid (non-fixed gender indentity that may change overtime)</t>
+    <t>Gender Fluid (non-fixed gender identity that may change over time)</t>
   </si>
   <si>
     <t>911541000124103</t>
@@ -170,7 +172,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-nullFlavor</t>
   </si>
 </sst>
 </file>
